--- a/logindata.xlsx
+++ b/logindata.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LearnPlaywright\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6935C0CF-05F3-41E5-96D0-9C1BC8EF92DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F6971C7-502B-4410-8B05-7E5E73182793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33765" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{1E4F73F3-ADFE-416F-9D13-ADEC12617EAC}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8880" xr2:uid="{1E4F73F3-ADFE-416F-9D13-ADEC12617EAC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t>Username</t>
   </si>
@@ -61,6 +61,15 @@
   </si>
   <si>
     <t>Telangana</t>
+  </si>
+  <si>
+    <t>abc</t>
+  </si>
+  <si>
+    <t>kljaklj@gmail.com</t>
+  </si>
+  <si>
+    <t>Karmanghat</t>
   </si>
 </sst>
 </file>
@@ -423,7 +432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73E54D22-4AA3-41F7-A3B8-7A3F3B7E1F26}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
@@ -466,10 +475,32 @@
         <v>11</v>
       </c>
     </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{CBBC64D4-A3AC-4E9C-A1C5-823501A6C112}"/>
     <hyperlink ref="D2" r:id="rId2" xr:uid="{644FEFF2-10D7-43DE-8198-8F552910F7D9}"/>
+    <hyperlink ref="B3" r:id="rId3" xr:uid="{63282B97-C884-4C90-BFB9-4DF0345940B1}"/>
+    <hyperlink ref="D3" r:id="rId4" xr:uid="{EB7B843A-C730-4457-ACEC-C0E18DD5726A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
